--- a/assets/binomial/practice/Probability Questions - Problem Set 5.xlsx
+++ b/assets/binomial/practice/Probability Questions - Problem Set 5.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox (Personal)\Courses\Teaching\FIN 203\FIN 203 Fall 2020\5 Binomial\3 Practice\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox (Personal)\Courses\Teaching\FIN 203\FIN 203 Fall 2020\S3 Online\assets\binomial\practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E43207-5487-4F6E-B877-5E3DC66EE598}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17AA56FF-CDB2-45FF-BD1F-09CB2AA8E26A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{982B2296-9A5B-456E-9723-4C163784B0D5}"/>
   </bookViews>
@@ -490,8 +490,8 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <f>0.5^3</f>
-        <v>0.125</v>
+        <f>1-0.5^3</f>
+        <v>0.875</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
